--- a/pyfeng/data/heston_benchmark.xlsx
+++ b/pyfeng/data/heston_benchmark.xlsx
@@ -1,37 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\PyFENG\pyfeng\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB839AB-0F3E-4939-BD53-0CAC98313770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146FEEE3-D51E-4F0F-AB58-D6085F0488ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13944" yWindow="96" windowWidth="13872" windowHeight="16560" tabRatio="743" xr2:uid="{CFD8C97F-677E-4081-BE35-9D7DB797B3CD}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20760" windowHeight="16560" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Param" sheetId="7" r:id="rId1"/>
-    <sheet name="1" sheetId="1" r:id="rId2"/>
-    <sheet name="2" sheetId="31" r:id="rId3"/>
-    <sheet name="3" sheetId="32" r:id="rId4"/>
-    <sheet name="4" sheetId="4" r:id="rId5"/>
-    <sheet name="5" sheetId="5" r:id="rId6"/>
-    <sheet name="6" sheetId="6" r:id="rId7"/>
+    <sheet name="Param" sheetId="1" r:id="rId1"/>
+    <sheet name="1" sheetId="2" r:id="rId2"/>
+    <sheet name="2" sheetId="3" r:id="rId3"/>
+    <sheet name="3" sheetId="4" r:id="rId4"/>
+    <sheet name="4" sheetId="5" r:id="rId5"/>
+    <sheet name="5" sheetId="6" r:id="rId6"/>
+    <sheet name="6" sheetId="7" r:id="rId7"/>
     <sheet name="7" sheetId="8" r:id="rId8"/>
-    <sheet name="8" sheetId="34" r:id="rId9"/>
-    <sheet name="9" sheetId="33" r:id="rId10"/>
-    <sheet name="10" sheetId="35" r:id="rId11"/>
-    <sheet name="11" sheetId="36" r:id="rId12"/>
-    <sheet name="12" sheetId="37" r:id="rId13"/>
+    <sheet name="8" sheetId="9" r:id="rId9"/>
+    <sheet name="9" sheetId="10" r:id="rId10"/>
+    <sheet name="10" sheetId="11" r:id="rId11"/>
+    <sheet name="11" sheetId="12" r:id="rId12"/>
+    <sheet name="12" sheetId="13" r:id="rId13"/>
+    <sheet name="13" sheetId="14" r:id="rId14"/>
+    <sheet name="14" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -39,68 +38,66 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
+  <si>
+    <t>Sheet</t>
+  </si>
   <si>
     <t>sigma</t>
   </si>
   <si>
+    <t>theta</t>
+  </si>
+  <si>
     <t>vov</t>
   </si>
   <si>
     <t>rho</t>
   </si>
   <si>
+    <t>mr</t>
+  </si>
+  <si>
     <t>texp</t>
   </si>
   <si>
+    <t>spot</t>
+  </si>
+  <si>
+    <t>intr</t>
+  </si>
+  <si>
+    <t>divr</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>nc</t>
+  </si>
+  <si>
+    <t>col_name</t>
+  </si>
+  <si>
     <t>Reference</t>
   </si>
   <si>
-    <t>col_name</t>
-  </si>
-  <si>
-    <t>spot</t>
-  </si>
-  <si>
-    <t>Sheet</t>
-  </si>
-  <si>
-    <t>theta</t>
-  </si>
-  <si>
-    <t>mr</t>
-  </si>
-  <si>
-    <t>intr</t>
+    <t>Table 2 (Case I) in Andersen (2008), Table 2, 3  (Case I) in Van Haastrecht &amp; Pelsser (2010), SV-II in Lord et al (2010), Case 1-3 in Tse &amp; Wan (2013)</t>
+  </si>
+  <si>
+    <t>Table 3 (Case II) in Andersen (2008), Table 2, 5  (Case III) in Van Haastrecht &amp; Pelsser (2010).</t>
+  </si>
+  <si>
+    <t>Table 2, 4  (Case II) in Van Haastrecht &amp; Pelsser (2010).</t>
   </si>
   <si>
     <t>Price</t>
@@ -109,22 +106,34 @@
     <t>Tables 1, 4 in Broadie &amp; Kaya (2006). Case 4 in Tse &amp; Wan (2013)</t>
   </si>
   <si>
+    <t>Tables 2, 5 in Broadie &amp; Kaya (2006), SV-I in Lord et al (2010), Case 5 in Tse &amp; Wan (2013)</t>
+  </si>
+  <si>
+    <t>Figure 6 in Kahl and Jäckel (2005, Wilmott).</t>
+  </si>
+  <si>
     <t>Smith (2007), Case 6 in Tse &amp; Wan (2013)</t>
   </si>
   <si>
-    <t>Tables 2, 5 in Broadie &amp; Kaya (2006), SV-I in Lord et al (2010), Case 5 in Tse &amp; Wan (2013)</t>
-  </si>
-  <si>
-    <t>Table 2, 4  (Case II) in Van Haastrecht &amp; Pelsser (2010).</t>
-  </si>
-  <si>
-    <t>Figure 6 in Kahl and Jäckel (2005, Wilmott).</t>
-  </si>
-  <si>
-    <t>df</t>
-  </si>
-  <si>
-    <t>nc</t>
+    <t>Lewis (2019) https://financepress.com/2019/02/15/heston-model-reference-prices/</t>
+  </si>
+  <si>
+    <t>Table A3, Figure 3 (Set I) in von Sydow et al. (2018). BENCHOP - SLV. https://doi.org/10.1080/00207160.2018.1544368</t>
+  </si>
+  <si>
+    <t>Exact</t>
+  </si>
+  <si>
+    <t>Table 1A in Ball &amp; Roma (1994)</t>
+  </si>
+  <si>
+    <t>Table 1B in Ball &amp; Roma (1994)</t>
+  </si>
+  <si>
+    <t>Table 4 (T=1) in Fang &amp; Oosterlee (2008)</t>
+  </si>
+  <si>
+    <t>Table 5 (T=10) in Fang &amp; Oosterlee (2008)</t>
   </si>
   <si>
     <t>Strike</t>
@@ -133,21 +142,6 @@
     <t>CP</t>
   </si>
   <si>
-    <t>divr</t>
-  </si>
-  <si>
-    <t>Table A3, Figure 3 (Set I) in von Sydow et al. (2018). BENCHOP - SLV. https://doi.org/10.1080/00207160.2018.1544368</t>
-  </si>
-  <si>
-    <t>Table 2 (Case I) in Andersen (2008), Table 2, 3  (Case I) in Van Haastrecht &amp; Pelsser (2010), SV-II in Lord et al (2010), Case 1-3 in Tse &amp; Wan (2013)</t>
-  </si>
-  <si>
-    <t>Table 3 (Case II) in Andersen (2008), Table 2, 5  (Case III) in Van Haastrecht &amp; Pelsser (2010).</t>
-  </si>
-  <si>
-    <t>Lewis (2019) https://financepress.com/2019/02/15/heston-model-reference-prices/</t>
-  </si>
-  <si>
     <t>BS</t>
   </si>
   <si>
@@ -155,15 +149,6 @@
   </si>
   <si>
     <t>OP3</t>
-  </si>
-  <si>
-    <t>Exact</t>
-  </si>
-  <si>
-    <t>Table 1A in Ball &amp; Roma (1994)</t>
-  </si>
-  <si>
-    <t>Table 1B in Ball &amp; Roma (1994)</t>
   </si>
 </sst>
 </file>
@@ -532,8 +517,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0584B610-149E-4DFB-B94E-F604CBCB4976}">
-  <dimension ref="A1:N13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
@@ -542,51 +527,51 @@
     <col min="9" max="9" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.77734375"/>
+    <col min="12" max="12" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
-      </c>
       <c r="L1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -622,19 +607,19 @@
         <v>0</v>
       </c>
       <c r="K2" s="6">
-        <f>4*C2*F2/(D2*D2)</f>
+        <f t="shared" ref="K2:K13" si="0">4*C2*F2/(D2*D2)</f>
         <v>0.08</v>
       </c>
       <c r="L2">
-        <f>4*B2*F2/(D2*D2)/(EXP(F2*G2)-1)</f>
+        <f t="shared" ref="L2:L13" si="1">4*B2*F2/(D2*D2)/(EXP(F2*G2)-1)</f>
         <v>5.4269239250433849E-4</v>
       </c>
-      <c r="M2" s="3" t="str" cm="1">
+      <c r="M2" s="3" t="str">
         <f t="array" aca="1" ref="M2" ca="1">INDIRECT(A2&amp;"!$B$1")</f>
         <v>Price</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -645,7 +630,7 @@
         <v>0.04</v>
       </c>
       <c r="C3" s="2">
-        <f t="shared" ref="C3" si="0">B3</f>
+        <f>B3</f>
         <v>0.04</v>
       </c>
       <c r="D3" s="2">
@@ -670,19 +655,19 @@
         <v>0</v>
       </c>
       <c r="K3" s="6">
-        <f>4*C3*F3/(D3*D3)</f>
+        <f t="shared" si="0"/>
         <v>5.9259259259259255E-2</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L13" si="1">4*B3*F3/(D3*D3)/(EXP(F3*G3)-1)</f>
+        <f t="shared" si="1"/>
         <v>6.6570623422136589E-4</v>
       </c>
-      <c r="M3" s="3" t="str" cm="1">
+      <c r="M3" s="3" t="str">
         <f t="array" aca="1" ref="M3" ca="1">INDIRECT(A3&amp;"!$B$1")</f>
         <v>Price</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -718,19 +703,19 @@
         <v>0</v>
       </c>
       <c r="K4" s="6">
-        <f t="shared" ref="K4:K10" si="2">4*C4*F4/(D4*D4)</f>
+        <f t="shared" si="0"/>
         <v>0.36</v>
       </c>
       <c r="L4">
         <f t="shared" si="1"/>
         <v>2.442115766269523E-3</v>
       </c>
-      <c r="M4" s="3" t="str" cm="1">
+      <c r="M4" s="3" t="str">
         <f t="array" aca="1" ref="M4" ca="1">INDIRECT(A4&amp;"!$B$1")</f>
         <v>Price</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -765,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.268368718086536</v>
       </c>
       <c r="L5">
@@ -773,10 +758,10 @@
         <v>1.3710061880287368E-3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -811,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
       <c r="L6">
@@ -819,10 +804,10 @@
         <v>3.2689433526975188E-5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -857,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.16</v>
       </c>
       <c r="L7">
@@ -865,10 +850,10 @@
         <v>7.2643185615500428E-6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -903,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.90353478515184005</v>
       </c>
       <c r="L8">
@@ -911,10 +896,10 @@
         <v>4.7291206987607939E-3</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -949,7 +934,7 @@
         <v>0.02</v>
       </c>
       <c r="K9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="L9">
@@ -957,10 +942,10 @@
         <v>1.1940710632815392E-2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -995,7 +980,7 @@
         <v>0.02</v>
       </c>
       <c r="K10" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="L10">
@@ -1003,10 +988,10 @@
         <v>3.9205333191116547</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1041,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="6">
-        <f t="shared" ref="K11:K13" si="3">4*C11*F11/(D11*D11)</f>
+        <f t="shared" si="0"/>
         <v>0.44375999999999999</v>
       </c>
       <c r="L11">
@@ -1049,10 +1034,10 @@
         <v>9.6455413114132763E-2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1087,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="L12">
@@ -1095,10 +1080,10 @@
         <v>1.4086587847469905</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1133,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>6.1249999999999991</v>
       </c>
       <c r="L13">
@@ -1141,36 +1126,128 @@
         <v>0.11427633222811603</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.57509999999999994</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-0.57110000000000005</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1.5768</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f t="shared" ref="K14:K15" si="2">4*C14*F14/(D14*D14)</f>
+        <v>0.75898455708458157</v>
+      </c>
+      <c r="L14">
+        <f t="shared" ref="L14:L15" si="3">4*B14*F14/(D14*D14)/(EXP(F14*G14)-1)</f>
+        <v>8.6919954412299952E-2</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.57509999999999994</v>
+      </c>
+      <c r="E15" s="2">
+        <v>-0.57110000000000005</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1.5768</v>
+      </c>
+      <c r="G15" s="2">
+        <v>10</v>
+      </c>
+      <c r="H15" s="2">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>0.75898455708458157</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="3"/>
+        <v>4.736227848470753E-8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N9" r:id="rId1" display="https://financepress.com/2019/02/15/heston-model-reference-prices/" xr:uid="{7031F408-D0C8-4303-980A-BE75B855310D}"/>
-    <hyperlink ref="N10" r:id="rId2" display="https://financepress.com/2019/02/15/heston-model-reference-prices/" xr:uid="{875806D3-0B48-4136-831B-3F4391F03BDC}"/>
+    <hyperlink ref="N9" r:id="rId1" display="https://financepress.com/2019/02/15/heston-model-reference-prices/" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N10" r:id="rId2" display="https://financepress.com/2019/02/15/heston-model-reference-prices/" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437B921E-6D3A-47EC-9DF4-CC9958C57C5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -1245,7 +1322,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE028F6-A224-4AC3-A0F7-14C744EB35E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1254,10 +1331,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1295,25 +1372,25 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E32A6B08-519D-4169-BF8E-2AEB29E981DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1407,7 +1484,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EED313-9C6E-4407-8CA8-ACB153FA9431}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1416,19 +1493,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1521,8 +1598,72 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>5.7851554500000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>22.318945791000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5761A8C7-5DBE-4514-94EE-A5933B58C928}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1531,10 +1672,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1575,16 +1716,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0F9FDE4-4755-4E32-814A-85CBF4499A47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1617,16 +1758,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FCD568-C350-4F53-ADA8-3A672B89280F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1659,7 +1800,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EF16E80-6FB9-4334-AC30-EE1DE9F72C5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1668,10 +1809,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1688,7 +1829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B796A2E3-3674-432B-9CAB-65F8F7D4F037}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1697,10 +1838,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1717,7 +1858,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D4134D2-54E5-4470-946C-B42F18CBD0D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1726,10 +1867,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1746,7 +1887,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF78B50E-A6E0-46A0-B3CB-216FA84D35EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1755,10 +1896,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1775,19 +1916,19 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B01345-7AC3-4EF6-AA31-75067E57E02B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
